--- a/docs/huong-dan/nhap-lieu-bang-excel/mau/mau-tieu-thu.xlsx
+++ b/docs/huong-dan/nhap-lieu-bang-excel/mau/mau-tieu-thu.xlsx
@@ -462,20 +462,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -512,45 +513,50 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
+          <t>Mã HĐ/PL</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
           <t>Nguồn mủ</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Loại HĐ</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Hình thức</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Loại mủ</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Số lượng</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Giá bán</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Giá bán bằng</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>Ngày xuất kho</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>Ngày xuất hoá đơn</t>
         </is>
@@ -565,33 +571,38 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
+          <t>số hợp đồng / phụ lục</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
           <t>để trống = mủ thu mua</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>tấn</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>triệu đ/tấn khi VND · USD/tấn khi USD</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>VND | USD</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>dd/mm/yyyy</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
         <is>
           <t>dd/mm/yyyy</t>
         </is>
@@ -603,19 +614,19 @@
     <dataValidation sqref="A7:A506" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='Danh mục'!$A$2:$A$40</formula1>
     </dataValidation>
-    <dataValidation sqref="C7:C506" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D7:D506" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Mủ thu mua,Mủ khai thác"</formula1>
     </dataValidation>
-    <dataValidation sqref="D7:D506" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E7:E506" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dài hạn,Chuyến"</formula1>
     </dataValidation>
-    <dataValidation sqref="E7:E506" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F7:F506" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"XK / UTXK,Nội tiêu"</formula1>
     </dataValidation>
-    <dataValidation sqref="F7:F506" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G7:G506" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SVR CV 50,SVR CV60,SVR L,SVR 3L Mix,SVR 3L,SVR 5S,SVR 5,SVR 10 Mix,SVR 10 / CSR 10,SVR 20 / CSR 20,RSS 3,RSS 1,LATEX,Skim Block,SVR 10CV / 20CV,Chủng loại khác"</formula1>
     </dataValidation>
-    <dataValidation sqref="I7:I506" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J7:J506" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"VND,USD"</formula1>
     </dataValidation>
   </dataValidations>
